--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487479_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487479_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4969</v>
+        <v>9.6013</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9955</v>
+        <v>8.539400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5014</v>
+        <v>1.0619</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3738</v>
+        <v>5.68</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9996</v>
+        <v>3.9014</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6259</v>
+        <v>1.7786</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5081</v>
+        <v>7.5581</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5381</v>
+        <v>4.8503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.97</v>
+        <v>2.7078</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1343</v>
+        <v>-1.8781</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5385</v>
+        <v>-0.9489</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5958</v>
+        <v>-0.9292</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9377</v>
+        <v>0.5875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1336</v>
+        <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8098</v>
+        <v>-0.2585</v>
       </c>
       <c r="T2" t="n">
-        <v>4.0322</v>
+        <v>0.0135</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7775</v>
+        <v>-0.272</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3756</v>
+        <v>3.5922</v>
       </c>
       <c r="W2" t="n">
-        <v>2.651</v>
+        <v>2.9263</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2754</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.5245</v>
+        <v>8.589</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5161</v>
+        <v>7.1301</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0084</v>
+        <v>1.4589</v>
       </c>
       <c r="G3" t="n">
-        <v>5.68</v>
+        <v>1.3738</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9014</v>
+        <v>1.9996</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7786</v>
+        <v>-0.6259</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5581</v>
+        <v>3.5081</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8503</v>
+        <v>2.5381</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7078</v>
+        <v>0.97</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8781</v>
+        <v>-2.1343</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9489</v>
+        <v>-0.5385</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9292</v>
+        <v>-1.5958</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5875</v>
+        <v>2.9377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R3" t="n">
-        <v>2.546</v>
+        <v>3.1336</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3353</v>
+        <v>1.9019</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0098</v>
+        <v>1.1669</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3255</v>
+        <v>0.735</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5922</v>
+        <v>2.3756</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9263</v>
+        <v>2.651</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.352</v>
+        <v>1.8286</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7897</v>
+        <v>0.892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5623</v>
+        <v>0.9366</v>
       </c>
       <c r="G4" t="n">
         <v>1.7559</v>
@@ -766,13 +766,13 @@
         <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9915</v>
+        <v>-0.5149</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4464</v>
+        <v>-0.3441</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5451</v>
+        <v>-0.1708</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4261</v>
+        <v>0.8446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8353</v>
+        <v>1.04</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4092</v>
+        <v>-0.1953</v>
       </c>
       <c r="G5" t="n">
         <v>0.7411</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7067</v>
+        <v>-0.2882</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0306</v>
+        <v>0.1741</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6761</v>
+        <v>-0.4623</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0163</v>
+        <v>0.5326</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2443</v>
+        <v>0.6536</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2279</v>
+        <v>-0.121</v>
       </c>
       <c r="G6" t="n">
         <v>1.0809</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3975</v>
+        <v>0.1188</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0594</v>
+        <v>0.3499</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3381</v>
+        <v>-0.2311</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4572</v>
+        <v>-0.3955</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4535</v>
+        <v>0.479</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8232</v>
+        <v>-0.2549</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7016</v>
+        <v>-1.9071</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1216</v>
+        <v>1.6522</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3545</v>
+        <v>1.821</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3641</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009599999999999999</v>
+        <v>2.7126</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4687</v>
+        <v>-2.076</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3375</v>
+        <v>-1.0156</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1313</v>
+        <v>-1.0604</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3709</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2497</v>
+        <v>-0.061</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1476</v>
+        <v>0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>0.102</v>
+        <v>-0.1857</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5507</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0943</v>
+        <v>-0.5982</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3862</v>
+        <v>0.1247</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2919</v>
+        <v>-0.7228</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2549</v>
+        <v>2.0703</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9071</v>
+        <v>0.883</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6522</v>
+        <v>1.1872</v>
       </c>
       <c r="J8" t="n">
-        <v>1.821</v>
+        <v>3.0672</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8915999999999999</v>
+        <v>1.082</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7126</v>
+        <v>1.9852</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.076</v>
+        <v>-0.9969</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0156</v>
+        <v>-0.199</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0604</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7598</v>
+        <v>-0.9231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.387</v>
+        <v>-0.4552</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3728</v>
+        <v>-0.4679</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2754</v>
+        <v>-1.5495</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6659</v>
+        <v>-0.3329</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3905</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5864</v>
+        <v>-1.0629</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4894</v>
+        <v>-1.1154</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0971</v>
+        <v>0.0526</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0703</v>
+        <v>-0.8232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.883</v>
+        <v>-0.7016</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1872</v>
+        <v>-0.1216</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0672</v>
+        <v>-0.3545</v>
       </c>
       <c r="K9" t="n">
-        <v>1.082</v>
+        <v>-0.3641</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9852</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9969</v>
+        <v>-0.4687</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.199</v>
+        <v>-0.3375</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1313</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9113</v>
+        <v>-0.356</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0692</v>
+        <v>-0.0571</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8421</v>
+        <v>-0.2989</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5495</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3329</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7371</v>
+        <v>-2.2329</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2978</v>
+        <v>-3.8688</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4394</v>
+        <v>1.6359</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1063</v>
+        <v>-2.5041</v>
       </c>
       <c r="H10" t="n">
-        <v>0.405</v>
+        <v>-0.4566</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5113</v>
+        <v>-2.0474</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1709</v>
+        <v>-2.2561</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6737</v>
+        <v>-0.5972</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8446</v>
+        <v>-1.6589</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9354</v>
+        <v>-0.248</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2687</v>
+        <v>0.1406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6667</v>
+        <v>-0.3886</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7483</v>
+        <v>-0.3532</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>-0.6334</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6583</v>
+        <v>0.2803</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6659</v>
+        <v>-0.5507</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6083</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7934</v>
+        <v>-2.7012</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4828</v>
+        <v>-2.5024</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6894</v>
+        <v>-0.1988</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5041</v>
+        <v>-2.1063</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4566</v>
+        <v>0.405</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0474</v>
+        <v>-2.5113</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2561</v>
+        <v>-1.1709</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5972</v>
+        <v>0.6737</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6589</v>
+        <v>-1.8446</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.248</v>
+        <v>-0.9354</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1406</v>
+        <v>-0.2687</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3886</v>
+        <v>-0.6667</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9137</v>
+        <v>-0.7124</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2474</v>
+        <v>-0.2947</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3337</v>
+        <v>-0.4177</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5507</v>
+        <v>-0.6659</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5507</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3289</v>
+        <v>-3.587</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3106</v>
+        <v>-2.5153</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0183</v>
+        <v>-1.0717</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7008</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0774</v>
+        <v>-0.3355</v>
       </c>
       <c r="T12" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2844</v>
+        <v>-0.3379</v>
       </c>
       <c r="V12" t="n">
         <v>0.0576</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8185</v>
+        <v>10.8184</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5033</v>
+        <v>7.503399999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>3.315</v>
+        <v>3.315300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>3.312699999999998</v>
@@ -1468,13 +1468,13 @@
         <v>21.5432</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.782</v>
+        <v>-1.7821</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0469999999999994</v>
+        <v>0.04690000000000025</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8292</v>
+        <v>-1.829</v>
       </c>
       <c r="V13" t="n">
         <v>2.4331</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8146</v>
+        <v>3.1297</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6464</v>
+        <v>1.3902</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1682</v>
+        <v>1.7395</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4002</v>
+        <v>5.3121</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9909</v>
+        <v>2.4271</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5907</v>
+        <v>2.885</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3045</v>
+        <v>5.2862</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1024</v>
+        <v>2.0126</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2021</v>
+        <v>3.2736</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8885</v>
+        <v>0.4145</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7927</v>
+        <v>-0.3886</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7834</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5122</v>
+        <v>0.3973</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3212</v>
+        <v>0.6869</v>
       </c>
       <c r="U14" t="n">
-        <v>0.191</v>
+        <v>-0.2897</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8811</v>
+        <v>-0.8171</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8811</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0579</v>
+        <v>2.7412</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7996</v>
+        <v>1.5997</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2583</v>
+        <v>1.1415</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3121</v>
+        <v>1.4002</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4271</v>
+        <v>1.9909</v>
       </c>
       <c r="I15" t="n">
-        <v>2.885</v>
+        <v>-0.5907</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2862</v>
+        <v>1.3045</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0126</v>
+        <v>1.1024</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2736</v>
+        <v>0.2021</v>
       </c>
       <c r="M15" t="n">
-        <v>0.026</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4145</v>
+        <v>0.8885</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3886</v>
+        <v>-0.7927</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3255</v>
+        <v>1.4387</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0963</v>
+        <v>1.2745</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7708</v>
+        <v>0.1642</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8171</v>
+        <v>-0.8811</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1512</v>
+        <v>-0.8811</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0038</v>
+        <v>2.3108</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1209</v>
+        <v>5.4279</v>
       </c>
       <c r="F16" t="n">
         <v>-3.1171</v>
@@ -1702,10 +1702,10 @@
         <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0112</v>
+        <v>0.2958</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3258</v>
+        <v>0.6328</v>
       </c>
       <c r="U16" t="n">
         <v>-0.337</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8456</v>
+        <v>1.6192</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5732</v>
+        <v>2.8012</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7276</v>
+        <v>-1.182</v>
       </c>
       <c r="G17" t="n">
         <v>0.9432</v>
@@ -1780,13 +1780,13 @@
         <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7523</v>
+        <v>0.0213</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.485</v>
+        <v>-0.257</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7328</v>
+        <v>0.2783</v>
       </c>
       <c r="V17" t="n">
         <v>1.0464</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6045</v>
+        <v>-2.9672</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6163999999999999</v>
+        <v>-4.4622</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2209</v>
+        <v>1.4951</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5342</v>
+        <v>-5.1222</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6727</v>
+        <v>-2.0403</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2069</v>
+        <v>-3.0819</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6271</v>
+        <v>-4.1326</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5059</v>
+        <v>-2.2475</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1212</v>
+        <v>-1.885</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1613</v>
+        <v>-0.9896</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8332</v>
+        <v>0.2073</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3281</v>
+        <v>-1.1969</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="S19" t="n">
-        <v>0.576</v>
+        <v>0.0221</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6516</v>
+        <v>-0.2341</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0756</v>
+        <v>0.2561</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8837</v>
+        <v>0.762</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.159</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6301</v>
+        <v>-3.272</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1786</v>
+        <v>0.0024</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5485</v>
+        <v>-3.2743</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.1222</v>
+        <v>-0.5342</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0403</v>
+        <v>0.6727</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0819</v>
+        <v>-1.2069</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.1326</v>
+        <v>2.6271</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2475</v>
+        <v>2.5059</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.885</v>
+        <v>0.1212</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9896</v>
+        <v>-3.1613</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2073</v>
+        <v>-1.8332</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1969</v>
+        <v>-1.3281</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3709</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6408</v>
+        <v>-0.0915</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9504</v>
+        <v>0.0376</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3096</v>
+        <v>-0.1291</v>
       </c>
       <c r="V20" t="n">
-        <v>0.762</v>
+        <v>-0.8837</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8837</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1217</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3341</v>
+        <v>-3.5818</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9593</v>
+        <v>-4.4477</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6252</v>
+        <v>0.8658</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6455</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5877</v>
+        <v>0.1645</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4752</v>
+        <v>0.0365</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1125</v>
+        <v>0.1281</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1217</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5759</v>
+        <v>-3.7435</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1735</v>
+        <v>-0.6619</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4024</v>
+        <v>-3.0816</v>
       </c>
       <c r="G22" t="n">
         <v>0.2053</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2518</v>
+        <v>-0.4193</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8316</v>
+        <v>-0.3199</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4202</v>
+        <v>-0.0994</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7875</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1163</v>
+        <v>-5.8021</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.543</v>
+        <v>-4.7476</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5733</v>
+        <v>-1.0545</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4663</v>
@@ -2248,13 +2248,13 @@
         <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1049</v>
+        <v>0.419</v>
       </c>
       <c r="T23" t="n">
-        <v>0.414</v>
+        <v>0.2094</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6908</v>
+        <v>0.2097</v>
       </c>
       <c r="V23" t="n">
         <v>0.3995</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.2661</v>
+        <v>-10.2928</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.216699999999999</v>
+        <v>-3.2168</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.0494</v>
+        <v>-7.0759</v>
       </c>
       <c r="G24" t="n">
         <v>-2.997700000000001</v>
@@ -2326,13 +2326,13 @@
         <v>14.6885</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0195</v>
+        <v>1.9926</v>
       </c>
       <c r="T24" t="n">
         <v>1.9479</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07169999999999987</v>
+        <v>0.04479999999999995</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4332</v>
